--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:50:07+00:00</t>
+    <t>2024-07-03T13:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:52:48+00:00</t>
+    <t>2024-07-03T13:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-03T13:54:46+00:00</t>
+    <t>2024-07-04T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-04T13:52:01+00:00</t>
+    <t>2024-07-09T12:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:16:32+00:00</t>
+    <t>2024-07-09T12:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T12:36:00+00:00</t>
+    <t>2024-07-12T14:55:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T14:55:46+00:00</t>
+    <t>2024-07-17T06:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:26:56+00:00</t>
+    <t>2024-07-17T06:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:40:14+00:00</t>
+    <t>2024-07-17T06:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T06:51:58+00:00</t>
+    <t>2024-07-17T17:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:08:26+00:00</t>
+    <t>2024-07-17T17:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T17:33:21+00:00</t>
+    <t>2024-07-18T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R314-TypeCre" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R314-TypeCre" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T16:11:48+00:00</t>
+    <t>2024-07-19T13:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T13:28:45+00:00</t>
+    <t>2024-07-19T14:51:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:03:17+00:00</t>
+    <t>2025-12-11T11:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T11:06:01+00:00</t>
+    <t>2026-05-06T06:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T06:43:41+00:00</t>
+    <t>2026-05-07T11:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:59:24+00:00</t>
+    <t>2026-06-15T13:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:14:04+00:00</t>
+    <t>2026-06-17T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:51:28+00:00</t>
+    <t>2026-06-22T16:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T16:38:09+00:00</t>
+    <t>2026-06-26T14:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:40:16+00:00</t>
+    <t>2026-06-29T13:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:29:33+00:00</t>
+    <t>2026-07-06T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T10:07:23+00:00</t>
+    <t>2026-07-06T12:34:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:34:55+00:00</t>
+    <t>2026-07-06T15:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T15:16:18+00:00</t>
+    <t>2026-07-09T08:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T08:50:24+00:00</t>
+    <t>2026-07-10T14:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T14:30:27+00:00</t>
+    <t>2026-07-15T07:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T07:07:52+00:00</t>
+    <t>2026-07-15T08:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:40:44+00:00</t>
+    <t>2026-07-17T08:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:17:39+00:00</t>
+    <t>2026-07-20T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T10:02:38+00:00</t>
+    <t>2026-08-18T14:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:54:32+00:00</t>
+    <t>2026-08-19T07:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T07:30:40+00:00</t>
+    <t>2026-08-19T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T11:37:26+00:00</t>
+    <t>2026-08-19T11:59:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T11:59:01+00:00</t>
+    <t>2026-08-20T07:20:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T07:20:42+00:00</t>
+    <t>2026-09-08T08:23:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:23:10+00:00</t>
+    <t>2026-09-10T10:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
+++ b/main/ig/ValueSet-sas-cpts-valueset-typecreneau.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:05:58+00:00</t>
+    <t>2026-09-11T14:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
